--- a/Config/Skill.xlsx
+++ b/Config/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3E429A-B9C8-4260-84A8-C5C87805035C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA3185A-0EBA-4704-BCEB-40D4AB9073A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="3645" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -459,6 +459,10 @@
   </si>
   <si>
     <t>飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法飞剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -812,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -1330,7 +1334,7 @@
         <v>10501</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7</v>
       </c>
@@ -1351,6 +1355,41 @@
       </c>
       <c r="K17">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2004</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>6103</v>
+      </c>
+      <c r="H18">
+        <v>200</v>
+      </c>
+      <c r="I18">
+        <v>20000</v>
+      </c>
+      <c r="J18">
+        <v>25000</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Skill.xlsx
+++ b/Config/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA3185A-0EBA-4704-BCEB-40D4AB9073A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573CE71D-6100-40CC-B123-D6ACD51D664B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="29890" windowHeight="16270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -463,6 +463,10 @@
   </si>
   <si>
     <t>施法飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能范围MM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +990,7 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="M4" t="s">
         <v>10</v>
@@ -1047,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -1088,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1132,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M8">
         <v>2</v>
@@ -1210,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M11">
         <v>130</v>
@@ -1380,16 +1384,16 @@
         <v>200</v>
       </c>
       <c r="I18">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J18">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Skill.xlsx
+++ b/Config/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573CE71D-6100-40CC-B123-D6ACD51D664B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF54141-DAE5-4C48-9BCD-6EF9BDB1DA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="29890" windowHeight="16270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通用被动技能（在角色创建时给自己添加buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>buffID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -467,6 +463,10 @@
   </si>
   <si>
     <t>技能范围MM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用被动技能（释放时给自己添加buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -857,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
         <v>32</v>
@@ -972,7 +972,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
         <v>43</v>
@@ -990,7 +990,7 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M4" t="s">
         <v>10</v>
@@ -1101,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -1173,7 +1173,7 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="J10">
         <v>10000</v>
@@ -1187,7 +1187,7 @@
         <v>1001</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1228,7 +1228,7 @@
         <v>10001</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1245,7 +1245,7 @@
         <v>20001002</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1291,7 +1291,7 @@
         <v>10002</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1308,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1343,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1600,10 +1600,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>51</v>
@@ -1614,10 +1614,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="28" x14ac:dyDescent="0.3">
@@ -1634,7 +1634,7 @@
         <v>54</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -1656,13 +1656,13 @@
         <v>2002</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>51</v>
@@ -1673,13 +1673,13 @@
         <v>10000</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Skill.xlsx
+++ b/Config/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF54141-DAE5-4C48-9BCD-6EF9BDB1DA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AA32E0-5D97-47A1-AA44-09BB70B1DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1053,9 +1053,6 @@
       <c r="L6">
         <v>1000</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
       <c r="N6">
         <v>1</v>
       </c>
@@ -1323,13 +1320,13 @@
         <v>6102</v>
       </c>
       <c r="H16" s="3">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="I16" s="3">
-        <v>1000</v>
+        <v>2367</v>
       </c>
       <c r="J16" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>

--- a/Config/Skill.xlsx
+++ b/Config/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AA32E0-5D97-47A1-AA44-09BB70B1DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBBE7A0-DC30-4CF1-A101-479FAA30BEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-945" windowWidth="21810" windowHeight="35145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K17">
         <v>0</v>
